--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_03C_2026.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_03C_2026.xlsx
@@ -930,6 +930,30 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="12" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="12" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="13" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -998,30 +1022,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="12" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="12" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="13" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1321,17 +1321,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="M1" s="78" t="s">
+      <c r="M1" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="86"/>
+      <c r="P1" s="86"/>
+      <c r="Q1" s="86"/>
+      <c r="R1" s="86"/>
+      <c r="S1" s="86"/>
+      <c r="T1" s="86"/>
+      <c r="U1" s="86"/>
       <c r="V1" s="17"/>
       <c r="W1" s="17"/>
       <c r="X1" s="17"/>
@@ -1360,9 +1360,9 @@
       <c r="U2" s="60"/>
     </row>
     <row r="3" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A3" s="65"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
+      <c r="A3" s="73"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
       <c r="D3" s="60"/>
       <c r="E3" s="60"/>
       <c r="F3" s="60"/>
@@ -1386,9 +1386,9 @@
       <c r="X3" s="13"/>
     </row>
     <row r="4" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A4" s="65"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
+      <c r="A4" s="73"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
       <c r="D4" s="59"/>
       <c r="E4" s="61"/>
       <c r="F4" s="61"/>
@@ -1434,156 +1434,156 @@
       <c r="U5" s="60"/>
     </row>
     <row r="6" spans="1:24" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A6" s="79"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79"/>
-      <c r="N6" s="79"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="79"/>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79"/>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="A6" s="87"/>
+      <c r="B6" s="87"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="87"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+      <c r="L6" s="87"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="87"/>
+      <c r="O6" s="87"/>
+      <c r="P6" s="87"/>
+      <c r="Q6" s="87"/>
+      <c r="R6" s="87"/>
+      <c r="S6" s="87"/>
+      <c r="T6" s="87"/>
+      <c r="U6" s="87"/>
       <c r="V6" s="15"/>
       <c r="W6" s="15"/>
       <c r="X6" s="15"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="M7" s="66" t="s">
+      <c r="M7" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="N7" s="66"/>
-      <c r="O7" s="66"/>
-      <c r="P7" s="66"/>
-      <c r="Q7" s="66"/>
-      <c r="R7" s="66"/>
-      <c r="S7" s="66"/>
-      <c r="T7" s="66"/>
-      <c r="U7" s="66"/>
+      <c r="N7" s="74"/>
+      <c r="O7" s="74"/>
+      <c r="P7" s="74"/>
+      <c r="Q7" s="74"/>
+      <c r="R7" s="74"/>
+      <c r="S7" s="74"/>
+      <c r="T7" s="74"/>
+      <c r="U7" s="74"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="75"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="80"/>
-      <c r="O8" s="81"/>
-      <c r="P8" s="82"/>
-      <c r="Q8" s="80"/>
-      <c r="R8" s="81"/>
-      <c r="S8" s="81"/>
-      <c r="T8" s="81"/>
-      <c r="U8" s="82"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="89"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="91"/>
+      <c r="K8" s="91"/>
+      <c r="L8" s="91"/>
+      <c r="M8" s="91"/>
+      <c r="N8" s="88"/>
+      <c r="O8" s="89"/>
+      <c r="P8" s="90"/>
+      <c r="Q8" s="88"/>
+      <c r="R8" s="89"/>
+      <c r="S8" s="89"/>
+      <c r="T8" s="89"/>
+      <c r="U8" s="90"/>
       <c r="V8" s="16"/>
       <c r="W8" s="16"/>
       <c r="X8" s="16"/>
     </row>
     <row r="9" spans="1:24" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="84"/>
-      <c r="B9" s="86"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="76"/>
-      <c r="E9" s="75" t="s">
+      <c r="A9" s="92"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="67"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="75" t="s">
+      <c r="F9" s="75"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="I9" s="67"/>
-      <c r="J9" s="68"/>
-      <c r="K9" s="69" t="s">
+      <c r="I9" s="75"/>
+      <c r="J9" s="76"/>
+      <c r="K9" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="L9" s="67"/>
-      <c r="M9" s="68"/>
-      <c r="N9" s="69" t="s">
+      <c r="L9" s="75"/>
+      <c r="M9" s="76"/>
+      <c r="N9" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="O9" s="67"/>
-      <c r="P9" s="68"/>
-      <c r="Q9" s="69" t="s">
+      <c r="O9" s="75"/>
+      <c r="P9" s="76"/>
+      <c r="Q9" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="R9" s="67"/>
-      <c r="S9" s="68"/>
-      <c r="T9" s="67"/>
-      <c r="U9" s="68"/>
+      <c r="R9" s="75"/>
+      <c r="S9" s="76"/>
+      <c r="T9" s="75"/>
+      <c r="U9" s="76"/>
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" s="84"/>
-      <c r="B10" s="86"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="72" t="s">
+      <c r="A10" s="92"/>
+      <c r="B10" s="94"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="72" t="s">
+      <c r="G10" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="76"/>
-      <c r="I10" s="72" t="s">
+      <c r="H10" s="84"/>
+      <c r="I10" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="72" t="s">
+      <c r="J10" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="K10" s="70"/>
-      <c r="L10" s="72" t="s">
+      <c r="K10" s="78"/>
+      <c r="L10" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="M10" s="72" t="s">
+      <c r="M10" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="N10" s="70"/>
-      <c r="O10" s="73" t="s">
+      <c r="N10" s="78"/>
+      <c r="O10" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="73" t="s">
+      <c r="P10" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="Q10" s="70"/>
-      <c r="R10" s="72" t="s">
+      <c r="Q10" s="78"/>
+      <c r="R10" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="S10" s="72" t="s">
+      <c r="S10" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="T10" s="73" t="s">
+      <c r="T10" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="U10" s="73" t="s">
+      <c r="U10" s="81" t="s">
         <v>6</v>
       </c>
       <c r="V10" s="12"/>
@@ -1591,27 +1591,27 @@
       <c r="X10" s="12"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" s="84"/>
-      <c r="B11" s="87"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="74"/>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="74"/>
-      <c r="U11" s="74"/>
+      <c r="A11" s="92"/>
+      <c r="B11" s="95"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="80"/>
+      <c r="M11" s="80"/>
+      <c r="N11" s="79"/>
+      <c r="O11" s="82"/>
+      <c r="P11" s="82"/>
+      <c r="Q11" s="79"/>
+      <c r="R11" s="80"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="82"/>
+      <c r="U11" s="82"/>
       <c r="V11" s="11"/>
       <c r="W11" s="11"/>
       <c r="X11" s="11"/>
@@ -5264,24 +5264,24 @@
       <c r="C65" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="D65" s="88"/>
-      <c r="E65" s="88"/>
-      <c r="F65" s="89"/>
-      <c r="G65" s="89"/>
-      <c r="H65" s="90"/>
-      <c r="I65" s="91"/>
-      <c r="J65" s="91"/>
-      <c r="K65" s="92"/>
-      <c r="L65" s="91"/>
-      <c r="M65" s="91"/>
-      <c r="N65" s="92"/>
-      <c r="O65" s="91"/>
-      <c r="P65" s="91"/>
-      <c r="Q65" s="92"/>
-      <c r="R65" s="91"/>
-      <c r="S65" s="91"/>
-      <c r="T65" s="91"/>
-      <c r="U65" s="91"/>
+      <c r="D65" s="65"/>
+      <c r="E65" s="65"/>
+      <c r="F65" s="66"/>
+      <c r="G65" s="66"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="68"/>
+      <c r="J65" s="68"/>
+      <c r="K65" s="69"/>
+      <c r="L65" s="68"/>
+      <c r="M65" s="68"/>
+      <c r="N65" s="69"/>
+      <c r="O65" s="68"/>
+      <c r="P65" s="68"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="68"/>
+      <c r="S65" s="68"/>
+      <c r="T65" s="68"/>
+      <c r="U65" s="68"/>
       <c r="V65" s="2"/>
       <c r="W65" s="2"/>
       <c r="X65" s="2"/>
@@ -5296,24 +5296,24 @@
       <c r="C66" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="D66" s="88"/>
-      <c r="E66" s="88"/>
-      <c r="F66" s="89"/>
-      <c r="G66" s="89"/>
-      <c r="H66" s="90"/>
-      <c r="I66" s="91"/>
-      <c r="J66" s="91"/>
-      <c r="K66" s="92"/>
-      <c r="L66" s="91"/>
-      <c r="M66" s="91"/>
-      <c r="N66" s="92"/>
-      <c r="O66" s="91"/>
-      <c r="P66" s="91"/>
-      <c r="Q66" s="92"/>
-      <c r="R66" s="91"/>
-      <c r="S66" s="91"/>
-      <c r="T66" s="91"/>
-      <c r="U66" s="91"/>
+      <c r="D66" s="65"/>
+      <c r="E66" s="65"/>
+      <c r="F66" s="66"/>
+      <c r="G66" s="66"/>
+      <c r="H66" s="67"/>
+      <c r="I66" s="68"/>
+      <c r="J66" s="68"/>
+      <c r="K66" s="69"/>
+      <c r="L66" s="68"/>
+      <c r="M66" s="68"/>
+      <c r="N66" s="69"/>
+      <c r="O66" s="68"/>
+      <c r="P66" s="68"/>
+      <c r="Q66" s="69"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="68"/>
+      <c r="T66" s="68"/>
+      <c r="U66" s="68"/>
       <c r="V66" s="2"/>
       <c r="W66" s="2"/>
       <c r="X66" s="2"/>
@@ -5666,7 +5666,7 @@
       <c r="C72" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="D72" s="93"/>
+      <c r="D72" s="70"/>
       <c r="E72" s="34"/>
       <c r="F72" s="58" t="str">
         <f t="shared" si="9"/>
@@ -5677,46 +5677,46 @@
         <v/>
       </c>
       <c r="H72" s="34"/>
-      <c r="I72" s="94" t="str">
+      <c r="I72" s="71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J72" s="94" t="str">
+      <c r="J72" s="71" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K72" s="95"/>
-      <c r="L72" s="94" t="str">
+      <c r="K72" s="72"/>
+      <c r="L72" s="71" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="M72" s="94" t="str">
+      <c r="M72" s="71" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N72" s="95"/>
-      <c r="O72" s="94" t="str">
+      <c r="N72" s="72"/>
+      <c r="O72" s="71" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="P72" s="94" t="str">
+      <c r="P72" s="71" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q72" s="95"/>
-      <c r="R72" s="94" t="str">
+      <c r="Q72" s="72"/>
+      <c r="R72" s="71" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="S72" s="94" t="str">
+      <c r="S72" s="71" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T72" s="94" t="str">
+      <c r="T72" s="71" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="U72" s="94" t="str">
+      <c r="U72" s="71" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -5767,6 +5767,6 @@
     <mergeCell ref="F10:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="33" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="25" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>